--- a/methods_comp_packages.xlsx
+++ b/methods_comp_packages.xlsx
@@ -172,7 +172,7 @@
     <t>Metabolomic data analysis</t>
   </si>
   <si>
-    <t>Notes：vegan: v2.6-8; phyloseq: v1.50.0; microeco (v1.13.0); The more "+" signs there are, the more functions/options are available, and the more situations it can be applied to.</t>
+    <t>Notes：vegan: v2.6-8; phyloseq: v1.50.0; microeco (v2.4.0); The more "+" signs there are, the more functions/options are available, and the more situations it can be applied to.</t>
   </si>
 </sst>
 </file>
